--- a/data/trans_orig/P19C09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>373683</t>
+          <t>374611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383791</t>
+          <t>384202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253943</t>
+          <t>252661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265364</t>
+          <t>265299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>632818</t>
+          <t>631574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647934</t>
+          <t>647130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>6840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22392</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286268</t>
+          <t>287375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298268</t>
+          <t>298282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317053</t>
+          <t>317271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328546</t>
+          <t>328551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>609343</t>
+          <t>609159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624583</t>
+          <t>624895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>22802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28420</t>
+          <t>28459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>405602</t>
+          <t>406424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422104</t>
+          <t>421826</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130257</t>
+          <t>130098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139067</t>
+          <t>138888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>540874</t>
+          <t>540835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558927</t>
+          <t>559191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38672</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27276</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52897</t>
+          <t>52699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830416</t>
+          <t>831592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>851837</t>
+          <t>852417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>574940</t>
+          <t>575901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589519</t>
+          <t>589852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1412439</t>
+          <t>1412637</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1438060</t>
+          <t>1437449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>38357</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230991</t>
+          <t>230957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242400</t>
+          <t>242423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>430708</t>
+          <t>431311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>446959</t>
+          <t>447462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>665156</t>
+          <t>664805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>685596</t>
+          <t>685914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28596</t>
+          <t>28005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51055</t>
+          <t>52331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30640</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57496</t>
+          <t>56659</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202357</t>
+          <t>202268</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210509</t>
+          <t>210545</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>892914</t>
+          <t>891638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>915373</t>
+          <t>915964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1098706</t>
+          <t>1099543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1125562</t>
+          <t>1124361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>49736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82872</t>
+          <t>82585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,82 +2805,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>86034</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>70230</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>106001</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>150323</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>124866</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>175572</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>86034</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>68598</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>104192</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>150323</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>128453</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>178874</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2361265</t>
+          <t>2361552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2393016</t>
+          <t>2394401</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,82 +2918,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2592</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>2650148</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2630181</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2665952</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>96,86%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,13%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>97,43%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>5029996</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>5004747</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5055453</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>96,61%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2592</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2650148</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2631990</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2667584</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,86%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,19%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>97,49%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>5029996</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>5001445</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>5051866</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012 (tasa de respuesta: 97,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33565</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360398</t>
+          <t>361101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373396</t>
+          <t>373450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>260504</t>
+          <t>262115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276860</t>
+          <t>277254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628224</t>
+          <t>628074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>648040</t>
+          <t>647628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>24386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>33174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356387</t>
+          <t>354973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>369035</t>
+          <t>368932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286540</t>
+          <t>286007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>303706</t>
+          <t>303753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649506</t>
+          <t>649192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>670171</t>
+          <t>670151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20633</t>
+          <t>19434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>14941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29508</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>504550</t>
+          <t>505749</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519315</t>
+          <t>520226</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224498</t>
+          <t>222652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234627</t>
+          <t>234629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733268</t>
+          <t>734721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>752649</t>
+          <t>752081</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22530</t>
+          <t>23357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26474</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41577</t>
+          <t>41312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929856</t>
+          <t>929029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945648</t>
+          <t>945499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>649016</t>
+          <t>648983</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>666509</t>
+          <t>665866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1586299</t>
+          <t>1586564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1608983</t>
+          <t>1609631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14156</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>23601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30669</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379401</t>
+          <t>380423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>392455</t>
+          <t>392497</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634839</t>
+          <t>634111</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>650306</t>
+          <t>650320</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1020600</t>
+          <t>1020804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1039942</t>
+          <t>1039786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,49 +5097,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>23885</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14852</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>35783</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>23885</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>14637</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>36118</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>17580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39981</t>
+          <t>39890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204938</t>
+          <t>204828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212496</t>
+          <t>212494</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,47 +5210,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>878511</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>866613</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>887544</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>96,03%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>827</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>878511</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>866278</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>887759</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>96,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1075817</t>
+          <t>1075908</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1097836</t>
+          <t>1098218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>36186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65961</t>
+          <t>64162</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67925</t>
+          <t>68284</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>108895</t>
+          <t>107982</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111992</t>
+          <t>111884</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161779</t>
+          <t>161929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2769794</t>
+          <t>2771593</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2800010</t>
+          <t>2799569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2957224</t>
+          <t>2958137</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2998194</t>
+          <t>2997835</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5740095</t>
+          <t>5739945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5789882</t>
+          <t>5789990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19165</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>369097</t>
+          <t>369759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383336</t>
+          <t>383083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296651</t>
+          <t>296591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310792</t>
+          <t>310685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670627</t>
+          <t>670772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690099</t>
+          <t>690387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>18846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25965</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303493</t>
+          <t>303104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314597</t>
+          <t>314644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315105</t>
+          <t>314729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328145</t>
+          <t>328662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>624267</t>
+          <t>624202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>641322</t>
+          <t>641118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18939</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386868</t>
+          <t>386272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399995</t>
+          <t>399309</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139421</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525632</t>
+          <t>525616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>538764</t>
+          <t>538886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>37128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>27454</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55702</t>
+          <t>56508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842952</t>
+          <t>842377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>863642</t>
+          <t>862969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656089</t>
+          <t>656577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674484</t>
+          <t>674054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507834</t>
+          <t>1507028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1533168</t>
+          <t>1533503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25494</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41886</t>
+          <t>41556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401727</t>
+          <t>402933</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417187</t>
+          <t>417386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>531987</t>
+          <t>532370</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548182</t>
+          <t>548708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>940764</t>
+          <t>941094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>962957</t>
+          <t>962781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33953</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46107</t>
+          <t>48103</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>222110</t>
+          <t>221218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235931</t>
+          <t>235889</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>791336</t>
+          <t>791685</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>811147</t>
+          <t>811118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1020730</t>
+          <t>1018734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1043129</t>
+          <t>1043589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94975</t>
+          <t>95442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59436</t>
+          <t>60078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95942</t>
+          <t>97426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129678</t>
+          <t>128410</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>178819</t>
+          <t>179762</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2560730</t>
+          <t>2560263</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2596558</t>
+          <t>2595848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2759671</t>
+          <t>2758187</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2796177</t>
+          <t>2795535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5332499</t>
+          <t>5331556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5381640</t>
+          <t>5382908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>15181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23597</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374611</t>
+          <t>374918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384202</t>
+          <t>384257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252661</t>
+          <t>253106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265299</t>
+          <t>265222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>631574</t>
+          <t>630993</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647130</t>
+          <t>646895</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287375</t>
+          <t>287560</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298282</t>
+          <t>298267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317271</t>
+          <t>317299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328551</t>
+          <t>328130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>609159</t>
+          <t>609364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624895</t>
+          <t>624813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28459</t>
+          <t>28751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406424</t>
+          <t>406667</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>421826</t>
+          <t>422621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130098</t>
+          <t>130430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138888</t>
+          <t>139063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>540835</t>
+          <t>540543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559191</t>
+          <t>558547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37496</t>
+          <t>37246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27887</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52699</t>
+          <t>50678</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831592</t>
+          <t>831842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>852417</t>
+          <t>852053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575901</t>
+          <t>574728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589852</t>
+          <t>589556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1412637</t>
+          <t>1414658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1437449</t>
+          <t>1438488</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38357</t>
+          <t>39780</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230957</t>
+          <t>229884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242423</t>
+          <t>242478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431311</t>
+          <t>429839</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>447462</t>
+          <t>446301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664805</t>
+          <t>663382</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>685914</t>
+          <t>686021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28005</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52331</t>
+          <t>50324</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56659</t>
+          <t>59149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202268</t>
+          <t>202154</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>210545</t>
+          <t>210524</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>891638</t>
+          <t>893645</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>915964</t>
+          <t>917475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1099543</t>
+          <t>1097053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1124361</t>
+          <t>1124912</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>49741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82585</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70230</t>
+          <t>67083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106001</t>
+          <t>105578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124866</t>
+          <t>126750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175572</t>
+          <t>176556</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2361552</t>
+          <t>2363113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2394401</t>
+          <t>2394396</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2630181</t>
+          <t>2630604</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2665952</t>
+          <t>2669099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5004747</t>
+          <t>5003763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5055453</t>
+          <t>5053569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18153</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>13788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33715</t>
+          <t>33406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361101</t>
+          <t>360834</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>373450</t>
+          <t>373437</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>262115</t>
+          <t>260754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277254</t>
+          <t>276946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628074</t>
+          <t>628383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>647628</t>
+          <t>648001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17000</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24386</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33174</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354973</t>
+          <t>356916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368932</t>
+          <t>369058</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286007</t>
+          <t>285867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>303753</t>
+          <t>303370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649192</t>
+          <t>646702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>670151</t>
+          <t>670177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14941</t>
+          <t>14732</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505749</t>
+          <t>505578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520226</t>
+          <t>519318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222652</t>
+          <t>222861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234629</t>
+          <t>234573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>734721</t>
+          <t>734279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>752081</t>
+          <t>751847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23357</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,47 +4411,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16578</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9095</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27061</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>16578</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9624</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26507</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929029</t>
+          <t>931559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945499</t>
+          <t>946583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,47 +4524,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>658912</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>648429</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>666395</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>97,55%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>658912</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>648983</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>665866</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1586564</t>
+          <t>1585530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1609631</t>
+          <t>1609385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23601</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>10652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30465</t>
+          <t>28662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380423</t>
+          <t>379614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>392497</t>
+          <t>391576</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>634111</t>
+          <t>634529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>650320</t>
+          <t>650305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1020804</t>
+          <t>1022607</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1039786</t>
+          <t>1040617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35783</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>39890</t>
+          <t>39107</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204828</t>
+          <t>204586</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212494</t>
+          <t>212484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>866613</t>
+          <t>867254</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>887544</t>
+          <t>886995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1075908</t>
+          <t>1076691</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1098218</t>
+          <t>1097966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36186</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64162</t>
+          <t>63383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68284</t>
+          <t>68684</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107982</t>
+          <t>104674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111884</t>
+          <t>111545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161929</t>
+          <t>158922</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2771593</t>
+          <t>2772372</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2799569</t>
+          <t>2801372</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2958137</t>
+          <t>2961445</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2997835</t>
+          <t>2997435</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5739945</t>
+          <t>5742952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5789990</t>
+          <t>5790329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32658</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>369759</t>
+          <t>369930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383083</t>
+          <t>382885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296591</t>
+          <t>296458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310685</t>
+          <t>310827</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>670772</t>
+          <t>671666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690387</t>
+          <t>690868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26030</t>
+          <t>26865</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303104</t>
+          <t>303536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314644</t>
+          <t>314604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314729</t>
+          <t>315259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328662</t>
+          <t>328285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>624202</t>
+          <t>623367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>641118</t>
+          <t>640399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19017</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386272</t>
+          <t>385895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>399309</t>
+          <t>399770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>525616</t>
+          <t>525006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>538886</t>
+          <t>538950</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37128</t>
+          <t>35442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56508</t>
+          <t>56758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842377</t>
+          <t>844063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862969</t>
+          <t>862945</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656577</t>
+          <t>656869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674054</t>
+          <t>674395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1507028</t>
+          <t>1506778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1533503</t>
+          <t>1533359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>25038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41556</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>402933</t>
+          <t>401242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>417386</t>
+          <t>417508</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532370</t>
+          <t>532443</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548708</t>
+          <t>548257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941094</t>
+          <t>940894</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>962781</t>
+          <t>962664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33604</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>46373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221218</t>
+          <t>222132</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235889</t>
+          <t>236006</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>791685</t>
+          <t>790741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>811118</t>
+          <t>810552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1018734</t>
+          <t>1020464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1043589</t>
+          <t>1043642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59857</t>
+          <t>61543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>95440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60078</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97426</t>
+          <t>95586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128410</t>
+          <t>128650</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179762</t>
+          <t>181229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2560263</t>
+          <t>2560265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2595848</t>
+          <t>2594162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2758187</t>
+          <t>2760027</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2795535</t>
+          <t>2796924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5331556</t>
+          <t>5330089</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5382908</t>
+          <t>5382668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
